--- a/temples.xlsx
+++ b/temples.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q152"/>
+  <dimension ref="A1:Q153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -9229,6 +9229,73 @@
       <c r="O152" s="2" t="inlineStr"/>
       <c r="P152" s="2" t="inlineStr"/>
       <c r="Q152" s="2" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Indian Community Centre (ICC Belfast)</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Belfast</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Northern Ireland</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Antrim</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>54.6069</v>
+      </c>
+      <c r="F153" t="n">
+        <v>-5.9361</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>86 Clifton St, Belfast BT13 1AB</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>+44 28 9024 9746</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Major Hindu community centre and temple, including a Tirupati (Balaji) shrine; hosts the annual Ramlila and Ravan Dahan.</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>Tue 6–7:30pm; Thu 6:30–7:30pm; Sat 6–7:30pm; Sun 5:30–6:30pm</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr"/>
+      <c r="O153" t="inlineStr"/>
+      <c r="P153" t="inlineStr"/>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:Q152"/>

--- a/temples.xlsx
+++ b/temples.xlsx
@@ -460,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q153"/>
+  <dimension ref="A1:Q154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -9277,7 +9277,6 @@
           <t>Major Hindu community centre and temple, including a Tirupati (Balaji) shrine; hosts the annual Ramlila and Ravan Dahan.</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr">
         <is>
           <t>Open</t>
@@ -9288,10 +9287,78 @@
           <t>Tue 6–7:30pm; Thu 6:30–7:30pm; Sat 6–7:30pm; Sun 5:30–6:30pm</t>
         </is>
       </c>
-      <c r="N153" t="inlineStr"/>
-      <c r="O153" t="inlineStr"/>
-      <c r="P153" t="inlineStr"/>
       <c r="Q153" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Sri Thurkkai Amman Temple</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Beeston</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>East Midlands</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Nottinghamshire</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>52.9192</v>
+      </c>
+      <c r="F154" t="n">
+        <v>-1.2021</v>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>10a West Cres, Beeston, Nottingham NG9 1QE</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>+44 115 967 7751</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Saiva</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Tamil temple dedicated to Durga (Thurkkai Amman), in a converted church in Beeston.</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>Daily 11am–2pm, 6–9pm</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>https://www.nottinghamamman.org</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr"/>
+      <c r="P154" t="inlineStr"/>
+      <c r="Q154" t="inlineStr">
         <is>
           <t>2026-07-08</t>
         </is>

--- a/temples.xlsx
+++ b/temples.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Temples" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Festivals" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Events" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Temples'!$A$1:$Q$152</definedName>
@@ -52,7 +53,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -62,6 +63,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002E4A6B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000E6B67"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -104,6 +110,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9933,7 +9942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -10157,6 +10166,134 @@
       <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Only enter a temple-specific date if the TEMPLE has published or confirmed it. Never infer one from the national date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>EVENTS SHEET (community calendar)</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>What it does</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Local festival events for towns WITHOUT a temple. They appear on that town's community page and vanish once the date passes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Date / End date</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>yyyy-mm-dd. End date only for multi-day events.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Must match a town set up as a community page. Currently: Cambridge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>e.g. 'Navratri Garba Night 3'</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Venue / Address</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Where it actually happens — hall, school, community centre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Organiser</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>The group running it. Always credit them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Their event page, Facebook post or booking link.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Poster</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Image filename you upload alongside the site, e.g. posters/hsn-navratri.jpg. OPTIONAL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Details</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>One or two lines. Keep event facts here as TEXT — text in a poster image cannot be found by Google.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>IMPORTANT</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Get the organiser's OK before hosting their poster, and always credit and link them.</t>
         </is>
       </c>
     </row>
@@ -10514,4 +10651,106 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="54" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>End date</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="E1" s="10" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="F1" s="10" t="inlineStr">
+        <is>
+          <t>Venue</t>
+        </is>
+      </c>
+      <c r="G1" s="10" t="inlineStr">
+        <is>
+          <t>Address</t>
+        </is>
+      </c>
+      <c r="H1" s="10" t="inlineStr">
+        <is>
+          <t>Organiser</t>
+        </is>
+      </c>
+      <c r="I1" s="10" t="inlineStr">
+        <is>
+          <t>Link</t>
+        </is>
+      </c>
+      <c r="J1" s="10" t="inlineStr">
+        <is>
+          <t>Poster</t>
+        </is>
+      </c>
+      <c r="K1" s="10" t="inlineStr">
+        <is>
+          <t>Details</t>
+        </is>
+      </c>
+      <c r="L1" s="10" t="inlineStr">
+        <is>
+          <t>Free?</t>
+        </is>
+      </c>
+      <c r="M1" s="10" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="N1" s="10" t="inlineStr">
+        <is>
+          <t>Checked</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>